--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/软件配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/软件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,11 +561,7 @@
           <t>人工录入</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>待客户确认</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -670,11 +666,7 @@
           <t>自动解析</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>已生成风险 R-002</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -748,6 +740,259 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>昇腾训练版本</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ascend Training Solution</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>24.0.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>昇腾推理版本</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ascend Inference Solution</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>24.0.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>操作系统</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FresBSD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>待客户确认</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CCAE AGENT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>iMaster CCAE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>V100R025C20SPC010</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>已生成风险 R-002</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CANN 8.0.1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/软件配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/软件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,11 +841,7 @@
           <t>人工录入</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>待客户确认</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -950,11 +946,7 @@
           <t>自动解析</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>已生成风险 R-002</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -993,6 +985,259 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>昇腾训练版本</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ascend Training Solution</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>24.0.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>昇腾推理版本</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ascend Inference Solution</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>24.0.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>操作系统</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FresBSD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>待客户确认</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CCAE AGENT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>iMaster CCAE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>V100R025C20SPC010</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>已生成风险 R-002</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CANN 8.0.1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/软件配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/软件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,7 +561,11 @@
           <t>人工录入</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>待客户确认</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -666,7 +670,11 @@
           <t>自动解析</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>已生成风险 R-002</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1086,11 +1094,7 @@
           <t>人工录入</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>待客户确认</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1195,11 +1199,7 @@
           <t>自动解析</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>已生成风险 R-002</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1238,6 +1238,251 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>昇腾训练版本</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ascend Training Solution</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>24.0.0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>昇腾推理版本</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ascend Inference Solution</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24.0.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>操作系统</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FresBSD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CCAE AGENT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>iMaster CCAE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>V100R025C20SPC010</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CANN 8.0.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
